--- a/modelo_templarios.xlsx
+++ b/modelo_templarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p59209\Downloads\Batalha_dos_Templarios_Site_READONLY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B2DE2D-E855-46ED-9503-6ECA4BCD627D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E377A0-09E5-4B3E-A6AD-3604F926F7AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
